--- a/luban-excels/xlsx/__enums__.xlsx
+++ b/luban-excels/xlsx/__enums__.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="449" uniqueCount="329">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="454" uniqueCount="334">
   <si>
     <t>##var</t>
   </si>
@@ -992,6 +992,12 @@
     <t>正式版</t>
   </si>
   <si>
+    <t>PlaytestRecording</t>
+  </si>
+  <si>
+    <t>Playtest录屏模式</t>
+  </si>
+  <si>
     <t>ERewardSelectionMode</t>
   </si>
   <si>
@@ -1014,6 +1020,15 @@
   </si>
   <si>
     <t>抽取时排除玩家此前从同一个盲盒中抽中的物品；其他盲盒抽中的同一道具不计入排除范围。（客户端盲盒专用，状态是否跨设备取决于云存档的最终设计）</t>
+  </si>
+  <si>
+    <t>RecordingSequence</t>
+  </si>
+  <si>
+    <t>录屏顺序发奖</t>
+  </si>
+  <si>
+    <t>直接按 RecordingRewardOrder 选择道具，不抽品质或权重。</t>
   </si>
 </sst>
 </file>
@@ -2003,7 +2018,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:L127"/>
+  <dimension ref="A1:L129"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.4"/>
   <cols>
     <col min="1" max="1" width="9.66666666666667" style="1" customWidth="1"/>
@@ -4193,43 +4208,68 @@
       </c>
     </row>
     <row r="126" spans="2:12">
-      <c r="B126" s="1" t="s">
+      <c r="H126" s="1" t="s">
         <v>321</v>
       </c>
-      <c r="C126" s="5" t="b">
+      <c r="I126" s="1" t="s">
+        <v>322</v>
+      </c>
+      <c r="J126" s="1">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="127" spans="2:12">
+      <c r="B127" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="C127" s="5" t="b">
         <v>0</v>
       </c>
-      <c r="D126" s="5" t="b">
+      <c r="D127" s="5" t="b">
         <v>1</v>
       </c>
-      <c r="F126" s="1" t="s">
-        <v>322</v>
-      </c>
-      <c r="H126" s="1" t="s">
-        <v>323</v>
-      </c>
-      <c r="I126" s="1" t="s">
+      <c r="F127" s="1" t="s">
         <v>324</v>
       </c>
-      <c r="J126" s="1">
+      <c r="H127" s="1" t="s">
+        <v>325</v>
+      </c>
+      <c r="I127" s="1" t="s">
+        <v>326</v>
+      </c>
+      <c r="J127" s="1">
         <v>1</v>
       </c>
-      <c r="K126" s="1" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="127" spans="2:12">
-      <c r="H127" s="1" t="s">
-        <v>326</v>
-      </c>
-      <c r="I127" s="1" t="s">
+      <c r="K127" s="1" t="s">
         <v>327</v>
       </c>
-      <c r="J127" s="1">
+    </row>
+    <row r="128" spans="2:12">
+      <c r="H128" s="1" t="s">
+        <v>328</v>
+      </c>
+      <c r="I128" s="1" t="s">
+        <v>329</v>
+      </c>
+      <c r="J128" s="1">
         <v>2</v>
       </c>
-      <c r="K127" s="1" t="s">
-        <v>328</v>
+      <c r="K128" s="1" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="129" spans="8:11">
+      <c r="H129" s="1" t="s">
+        <v>331</v>
+      </c>
+      <c r="I129" s="1" t="s">
+        <v>332</v>
+      </c>
+      <c r="J129" s="1">
+        <v>3</v>
+      </c>
+      <c r="K129" s="1" t="s">
+        <v>333</v>
       </c>
     </row>
   </sheetData>
